--- a/esyluban/examples/dev/DataTables/tag_datas/tag.xlsx
+++ b/esyluban/examples/dev/DataTables/tag_datas/tag.xlsx
@@ -419,7 +419,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="tag.TbTestTag" &amp; value_type="tag.TestTag" &amp; read_schema_from_file="false" &amp; input="tag_datas" &amp; output="tag_tbtesttag"</t>
+          <t>full_name="tag.TbTestTag" &amp; input="tag_datas"</t>
         </is>
       </c>
     </row>
